--- a/docs/backend_기능명세서.xlsx
+++ b/docs/backend_기능명세서.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="843">
   <si>
     <t>ID</t>
   </si>
@@ -247,6 +247,12 @@
     <t>검증 실패 시 422 + 오류 목록</t>
   </si>
   <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>scenarios/&lt;id&gt;/ 파일 저장 (DB 도입 전). 검증 실패 422 + issues, ID 중복 409</t>
+  </si>
+  <si>
     <t>BE-SCN-02</t>
   </si>
   <si>
@@ -283,6 +289,9 @@
     <t>비공개는 제작자만, 링크공유는 토큰 필요</t>
   </si>
   <si>
+    <t>메타(제목, 버전, 공개 범위, 검증 상태). 평점/플레이 통계는 미포함</t>
+  </si>
+  <si>
     <t>BE-SCN-04</t>
   </si>
   <si>
@@ -304,6 +313,9 @@
     <t>플레이어에게 비밀/엔딩 노출 방지</t>
   </si>
   <si>
+    <t>{ record, source }. TODO: 제작자만 조회</t>
+  </si>
+  <si>
     <t>BE-SCN-05</t>
   </si>
   <si>
@@ -319,6 +331,9 @@
     <t>진행 중 세션은 기존 버전 유지</t>
   </si>
   <si>
+    <t>검증 통과 시 이전 버전을 .versions/&lt;n&gt;.yaml 로 보관하고 버전 증가. meta.id 변경 불가</t>
+  </si>
+  <si>
     <t>BE-SCN-06</t>
   </si>
   <si>
@@ -331,6 +346,9 @@
     <t>DELETE</t>
   </si>
   <si>
+    <t>.trash/&lt;id&gt;-&lt;시각&gt; 로 이동 (소프트 삭제)</t>
+  </si>
+  <si>
     <t>BE-SCN-07</t>
   </si>
   <si>
@@ -343,6 +361,12 @@
     <t>/api/v1/users/me/scenarios</t>
   </si>
   <si>
+    <t>부분</t>
+  </si>
+  <si>
+    <t>인증이 없어 scenarios 폴더 전체를 반환</t>
+  </si>
+  <si>
     <t>BE-SCN-08</t>
   </si>
   <si>
@@ -361,6 +385,9 @@
     <t>multipart, 최대 5MB, zip bomb 방지</t>
   </si>
   <si>
+    <t>multipart 대신 application/zip 본문. 5MB, 항목 50개, scenario.yaml 1MB 제한</t>
+  </si>
+  <si>
     <t>BE-SCN-09</t>
   </si>
   <si>
@@ -373,6 +400,9 @@
     <t>/api/v1/scenarios/:scenarioId/export</t>
   </si>
   <si>
+    <t>scenario.yaml 하나를 담은 zip</t>
+  </si>
+  <si>
     <t>BE-SCN-10</t>
   </si>
   <si>
@@ -391,9 +421,6 @@
     <t>오류: { path, line, message, severity }</t>
   </si>
   <si>
-    <t>완료</t>
-  </si>
-  <si>
     <t>Zod 스키마 + 참조 무결성 + 줄 번호. CLI: npm run validate:scenario</t>
   </si>
   <si>
@@ -412,6 +439,9 @@
     <t>캐시 가능</t>
   </si>
   <si>
+    <t>Zod 스키마에서 zod-to-json-schema 로 생성</t>
+  </si>
+  <si>
     <t>BE-SCN-12</t>
   </si>
   <si>
@@ -442,10 +472,7 @@
     <t>/api/v1/scenarios/:scenarioId/test-sessions</t>
   </si>
   <si>
-    <t>부분</t>
-  </si>
-  <si>
-    <t>1인 플레이 API(POST /api/v1/play/games)로 대체 구현. 세션/인증 미연동</t>
+    <t>1인 플레이 게임 생성 (play.routes.ts). 응답은 POST /play/games 와 같음</t>
   </si>
   <si>
     <t>BE-SCN-14</t>
@@ -466,7 +493,7 @@
     <t>일반 세션에서는 403</t>
   </si>
   <si>
-    <t>주사위 고정만 (PATCH /api/v1/play/games/:gameId/debug)</t>
+    <t>1인 테스트 플레이는 PATCH /api/v1/play/games/:gameId/debug 로 구현 (주사위·플래그·변수·HP·순간이동·아이템). 멀티플레이 세션용은 미구현</t>
   </si>
   <si>
     <t>BE-SCN-15</t>
@@ -484,6 +511,9 @@
     <t>/api/v1/scenarios/:scenarioId/versions</t>
   </si>
   <si>
+    <t>버전 파일은 보관됨. 목록 API 없음</t>
+  </si>
+  <si>
     <t>BE-SCN-16</t>
   </si>
   <si>
@@ -511,6 +541,9 @@
     <t>/api/v1/scenarios/:scenarioId/visibility</t>
   </si>
   <si>
+    <t>설정 저장. 인증이 없어 접근 제한은 아직 없음</t>
+  </si>
+  <si>
     <t>BE-SCN-18</t>
   </si>
   <si>
@@ -1906,13 +1939,16 @@
     <t>BE-PLAY-05</t>
   </si>
   <si>
-    <t>주사위 고정</t>
-  </si>
-  <si>
-    <t>d20 고정값 설정/해제 (테스트용)</t>
+    <t>테스트 디버그</t>
+  </si>
+  <si>
+    <t>주사위 고정, 플래그/변수/HP 설정, 장면 순간이동, 아이템 지급. 응답 { view, entry }</t>
   </si>
   <si>
     <t>/api/v1/play/games/:gameId/debug</t>
+  </si>
+  <si>
+    <t>명세 외 추가 (1인 플레이). BE-SCN-14 의 1인용 구현</t>
   </si>
   <si>
     <t>BE-PLAY-06</t>
@@ -2556,7 +2592,7 @@
       <color rgb="FF0E7C86"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2575,7 +2611,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
+        <fgColor rgb="FFFFF1CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2586,11 +2622,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5F0DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF1CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2631,7 +2662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2672,10 +2703,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2684,7 +2712,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3498,27 +3526,27 @@
         <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>17</v>
@@ -3527,13 +3555,13 @@
         <v>43</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>22</v>
@@ -3544,19 +3572,19 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>17</v>
@@ -3565,36 +3593,36 @@
         <v>43</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>17</v>
@@ -3603,62 +3631,62 @@
         <v>43</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>71</v>
@@ -3667,36 +3695,36 @@
         <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>71</v>
@@ -3705,10 +3733,10 @@
         <v>72</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>17</v>
@@ -3717,7 +3745,7 @@
         <v>43</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>25</v>
@@ -3726,27 +3754,27 @@
         <v>33</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>17</v>
@@ -3755,36 +3783,36 @@
         <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>17</v>
@@ -3793,36 +3821,36 @@
         <v>43</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>17</v>
@@ -3831,36 +3859,36 @@
         <v>18</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>17</v>
@@ -3869,36 +3897,36 @@
         <v>43</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>42</v>
@@ -3907,10 +3935,10 @@
         <v>43</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>33</v>
@@ -3924,19 +3952,19 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>17</v>
@@ -3945,36 +3973,36 @@
         <v>18</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K24" s="14" t="s">
-        <v>142</v>
+      <c r="K24" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>17</v>
@@ -3983,36 +4011,36 @@
         <v>58</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>142</v>
+        <v>158</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>42</v>
@@ -4021,36 +4049,36 @@
         <v>43</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>42</v>
@@ -4059,10 +4087,10 @@
         <v>43</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>33</v>
@@ -4076,19 +4104,19 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>17</v>
@@ -4097,36 +4125,36 @@
         <v>58</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>42</v>
@@ -4135,7 +4163,7 @@
         <v>43</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>20</v>
@@ -4152,34 +4180,34 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>173</v>
+        <v>183</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>22</v>
@@ -4190,19 +4218,19 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>42</v>
@@ -4211,7 +4239,7 @@
         <v>18</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>25</v>
@@ -4228,19 +4256,19 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>42</v>
@@ -4249,7 +4277,7 @@
         <v>43</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>20</v>
@@ -4266,19 +4294,19 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>42</v>
@@ -4287,10 +4315,10 @@
         <v>43</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>33</v>
@@ -4304,31 +4332,31 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>33</v>
@@ -4342,34 +4370,34 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>173</v>
+        <v>205</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>22</v>
@@ -4380,34 +4408,34 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>22</v>
@@ -4418,19 +4446,19 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>17</v>
@@ -4439,7 +4467,7 @@
         <v>43</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>25</v>
@@ -4456,28 +4484,28 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>25</v>
@@ -4494,19 +4522,19 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>42</v>
@@ -4515,13 +4543,13 @@
         <v>43</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>22</v>
@@ -4532,19 +4560,19 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>17</v>
@@ -4553,13 +4581,13 @@
         <v>43</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>22</v>
@@ -4570,34 +4598,34 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="16" t="s">
-        <v>226</v>
+      <c r="G41" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>22</v>
@@ -4608,34 +4636,34 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="16" t="s">
-        <v>226</v>
+      <c r="G42" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>22</v>
@@ -4646,19 +4674,19 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>42</v>
@@ -4667,7 +4695,7 @@
         <v>43</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>25</v>
@@ -4684,19 +4712,19 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>42</v>
@@ -4705,340 +4733,340 @@
         <v>43</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>22</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="16" t="s">
-        <v>226</v>
+      <c r="G45" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="16" t="s">
-        <v>226</v>
+      <c r="G46" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="16" t="s">
-        <v>226</v>
+      <c r="G47" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G48" s="16" t="s">
-        <v>226</v>
+      <c r="G48" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="16" t="s">
-        <v>226</v>
+      <c r="G49" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G50" s="16" t="s">
-        <v>226</v>
+      <c r="G50" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G51" s="16" t="s">
-        <v>226</v>
+      <c r="G51" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K51" s="14" t="s">
-        <v>142</v>
+      <c r="K51" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G52" s="16" t="s">
-        <v>226</v>
+      <c r="G52" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>142</v>
+        <v>308</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>17</v>
@@ -5047,13 +5075,13 @@
         <v>43</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>22</v>
@@ -5064,34 +5092,34 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>173</v>
+        <v>320</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>22</v>
@@ -5102,259 +5130,259 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G55" s="16" t="s">
-        <v>226</v>
+      <c r="G55" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G56" s="16" t="s">
-        <v>226</v>
+      <c r="G56" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G57" s="16" t="s">
-        <v>226</v>
+      <c r="G57" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="J58" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="K58" s="14" t="s">
-        <v>142</v>
+        <v>349</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G59" s="16" t="s">
-        <v>226</v>
+      <c r="G59" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K59" s="14" t="s">
-        <v>142</v>
+      <c r="K59" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="16" t="s">
-        <v>226</v>
+      <c r="G60" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K60" s="14" t="s">
-        <v>142</v>
+      <c r="K60" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>226</v>
+        <v>366</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>33</v>
@@ -5368,31 +5396,31 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="16" t="s">
-        <v>226</v>
+      <c r="G62" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>33</v>
@@ -5406,57 +5434,57 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G63" s="16" t="s">
-        <v>226</v>
+      <c r="G63" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>42</v>
@@ -5465,48 +5493,48 @@
         <v>58</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>22</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G65" s="16" t="s">
-        <v>226</v>
+      <c r="G65" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>33</v>
@@ -5520,19 +5548,19 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>17</v>
@@ -5541,7 +5569,7 @@
         <v>43</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>20</v>
@@ -5553,24 +5581,24 @@
         <v>22</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>17</v>
@@ -5579,7 +5607,7 @@
         <v>43</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>20</v>
@@ -5591,24 +5619,24 @@
         <v>22</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="D68" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>17</v>
@@ -5617,36 +5645,36 @@
         <v>18</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="K68" s="7" t="s">
         <v>22</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>17</v>
@@ -5655,10 +5683,10 @@
         <v>58</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>33</v>
@@ -5672,19 +5700,19 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>17</v>
@@ -5693,13 +5721,13 @@
         <v>43</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="K70" s="7" t="s">
         <v>22</v>
@@ -5710,19 +5738,19 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>42</v>
@@ -5731,10 +5759,10 @@
         <v>43</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>33</v>
@@ -5748,28 +5776,28 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>173</v>
+        <v>430</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>25</v>
@@ -5786,28 +5814,28 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>173</v>
+        <v>434</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>25</v>
@@ -5824,19 +5852,19 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>17</v>
@@ -5845,13 +5873,13 @@
         <v>18</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="K74" s="7" t="s">
         <v>22</v>
@@ -5862,19 +5890,19 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>17</v>
@@ -5883,7 +5911,7 @@
         <v>43</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>20</v>
@@ -5900,19 +5928,19 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>17</v>
@@ -5921,10 +5949,10 @@
         <v>43</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>33</v>
@@ -5938,19 +5966,19 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>17</v>
@@ -5959,13 +5987,13 @@
         <v>58</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="K77" s="7" t="s">
         <v>22</v>
@@ -5976,19 +6004,19 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>17</v>
@@ -5997,7 +6025,7 @@
         <v>43</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>20</v>
@@ -6014,19 +6042,19 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>17</v>
@@ -6035,10 +6063,10 @@
         <v>18</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>33</v>
@@ -6052,19 +6080,19 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>42</v>
@@ -6073,10 +6101,10 @@
         <v>18</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>33</v>
@@ -6090,19 +6118,19 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>17</v>
@@ -6111,13 +6139,13 @@
         <v>18</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>22</v>
@@ -6128,19 +6156,19 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>17</v>
@@ -6149,13 +6177,13 @@
         <v>18</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="K82" s="7" t="s">
         <v>22</v>
@@ -6166,19 +6194,19 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>17</v>
@@ -6187,13 +6215,13 @@
         <v>18</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>22</v>
@@ -6204,69 +6232,69 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G84" s="17" t="s">
-        <v>336</v>
+      <c r="G84" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="K84" s="7" t="s">
         <v>22</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G85" s="17" t="s">
-        <v>336</v>
+      <c r="G85" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>33</v>
@@ -6275,36 +6303,36 @@
         <v>22</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G86" s="17" t="s">
-        <v>336</v>
+      <c r="G86" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>33</v>
@@ -6318,31 +6346,31 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G87" s="17" t="s">
-        <v>336</v>
+      <c r="G87" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>33</v>
@@ -6356,19 +6384,19 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>17</v>
@@ -6377,13 +6405,13 @@
         <v>43</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="K88" s="7" t="s">
         <v>22</v>
@@ -6394,19 +6422,19 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>17</v>
@@ -6415,10 +6443,10 @@
         <v>43</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>33</v>
@@ -6432,34 +6460,34 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G90" s="17" t="s">
-        <v>336</v>
+      <c r="G90" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="K90" s="7" t="s">
         <v>22</v>
@@ -6470,31 +6498,31 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>226</v>
+        <v>526</v>
+      </c>
+      <c r="F91" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>33</v>
@@ -6508,19 +6536,19 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>42</v>
@@ -6529,13 +6557,13 @@
         <v>18</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="K92" s="7" t="s">
         <v>22</v>
@@ -6546,31 +6574,31 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G93" s="17" t="s">
-        <v>336</v>
+      <c r="G93" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>33</v>
@@ -6584,31 +6612,31 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G94" s="17" t="s">
-        <v>336</v>
+      <c r="G94" s="16" t="s">
+        <v>347</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>33</v>
@@ -6622,28 +6650,28 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F95" s="15" t="s">
-        <v>173</v>
+        <v>547</v>
+      </c>
+      <c r="F95" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>25</v>
@@ -6660,19 +6688,19 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>17</v>
@@ -6681,10 +6709,10 @@
         <v>18</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>33</v>
@@ -6698,19 +6726,19 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>17</v>
@@ -6719,10 +6747,10 @@
         <v>18</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J97" s="3" t="s">
         <v>33</v>
@@ -6736,19 +6764,19 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>17</v>
@@ -6757,7 +6785,7 @@
         <v>43</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>25</v>
@@ -6774,19 +6802,19 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>17</v>
@@ -6795,10 +6823,10 @@
         <v>18</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>33</v>
@@ -6812,19 +6840,19 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>17</v>
@@ -6833,10 +6861,10 @@
         <v>43</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>33</v>
@@ -6850,19 +6878,19 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>17</v>
@@ -6871,10 +6899,10 @@
         <v>43</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>33</v>
@@ -6888,19 +6916,19 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>42</v>
@@ -6909,10 +6937,10 @@
         <v>43</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>33</v>
@@ -6926,19 +6954,19 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>42</v>
@@ -6947,13 +6975,13 @@
         <v>18</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="K103" s="7" t="s">
         <v>22</v>
@@ -6964,19 +6992,19 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>42</v>
@@ -6985,7 +7013,7 @@
         <v>18</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>25</v>
@@ -7002,19 +7030,19 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>42</v>
@@ -7023,10 +7051,10 @@
         <v>43</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>33</v>
@@ -7040,19 +7068,19 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>42</v>
@@ -7061,10 +7089,10 @@
         <v>58</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>33</v>
@@ -7078,19 +7106,19 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>42</v>
@@ -7099,10 +7127,10 @@
         <v>58</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J107" s="3" t="s">
         <v>33</v>
@@ -7116,19 +7144,19 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>42</v>
@@ -7137,10 +7165,10 @@
         <v>58</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>33</v>
@@ -7154,19 +7182,19 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>42</v>
@@ -7175,10 +7203,10 @@
         <v>58</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>33</v>
@@ -7192,19 +7220,19 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>42</v>
@@ -7213,10 +7241,10 @@
         <v>43</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>33</v>
@@ -7230,19 +7258,19 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>17</v>
@@ -7251,36 +7279,36 @@
         <v>43</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>17</v>
@@ -7289,36 +7317,36 @@
         <v>43</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="K112" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>17</v>
@@ -7327,36 +7355,36 @@
         <v>18</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>17</v>
@@ -7365,36 +7393,36 @@
         <v>43</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>17</v>
@@ -7403,36 +7431,36 @@
         <v>58</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>17</v>
@@ -7441,19 +7469,19 @@
         <v>18</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -7479,13 +7507,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
@@ -7505,71 +7533,71 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="18" t="s">
-        <v>644</v>
+      <c r="G2" s="17" t="s">
+        <v>656</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="18" t="s">
-        <v>644</v>
+      <c r="G3" s="17" t="s">
+        <v>656</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>17</v>
@@ -7583,123 +7611,123 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>644</v>
+      <c r="G5" s="17" t="s">
+        <v>656</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>656</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>644</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>644</v>
+      <c r="G7" s="17" t="s">
+        <v>656</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>460</v>
-      </c>
       <c r="F8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="18" t="s">
-        <v>644</v>
+      <c r="G8" s="17" t="s">
+        <v>656</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>17</v>
@@ -7713,19 +7741,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>17</v>
@@ -7739,19 +7767,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>17</v>
@@ -7765,19 +7793,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>17</v>
@@ -7791,19 +7819,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>17</v>
@@ -7817,19 +7845,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>17</v>
@@ -7843,71 +7871,71 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>142</v>
+      <c r="G15" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>142</v>
+      <c r="G16" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>17</v>
@@ -7921,97 +7949,97 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>142</v>
+      <c r="G18" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>142</v>
+      <c r="G19" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="14" t="s">
-        <v>142</v>
+      <c r="G20" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>42</v>
@@ -8025,19 +8053,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>42</v>
@@ -8051,19 +8079,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>17</v>
@@ -8077,19 +8105,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>17</v>
@@ -8103,19 +8131,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>42</v>
@@ -8129,19 +8157,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>42</v>
@@ -8155,19 +8183,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>42</v>
@@ -8181,19 +8209,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>42</v>
@@ -8207,19 +8235,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>42</v>
@@ -8233,19 +8261,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>42</v>
@@ -8259,19 +8287,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>17</v>
@@ -8285,19 +8313,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>17</v>
@@ -8311,54 +8339,54 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="14" t="s">
-        <v>142</v>
+      <c r="G33" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="18" t="s">
-        <v>644</v>
+      <c r="G34" s="17" t="s">
+        <v>656</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -8384,16 +8412,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -8407,19 +8435,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>22</v>
@@ -8430,19 +8458,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>22</v>
@@ -8453,19 +8481,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -8476,19 +8504,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -8499,19 +8527,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
@@ -8522,19 +8550,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -8545,19 +8573,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -8568,19 +8596,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -8591,19 +8619,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
@@ -8614,13 +8642,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>33</v>
@@ -8637,16 +8665,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>33</v>
@@ -8660,16 +8688,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>33</v>
@@ -8683,19 +8711,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -8706,16 +8734,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>33</v>
@@ -8729,19 +8757,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
@@ -8752,19 +8780,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
@@ -8775,19 +8803,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
@@ -8798,13 +8826,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>33</v>
@@ -8821,19 +8849,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
@@ -8844,16 +8872,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>33</v>
@@ -8867,13 +8895,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>33</v>
@@ -8890,16 +8918,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>33</v>
@@ -8913,19 +8941,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>22</v>
@@ -8936,13 +8964,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>33</v>
@@ -8959,16 +8987,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>33</v>
@@ -8982,19 +9010,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>22</v>
@@ -9005,19 +9033,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -9028,19 +9056,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -9061,80 +9089,80 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" style="19" customWidth="1"/>
+    <col min="1" max="1" width="18" style="18" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>818</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>819</v>
+      <c r="A1" s="19" t="s">
+        <v>830</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>831</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>820</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>821</v>
+      <c r="A2" s="19" t="s">
+        <v>832</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>822</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>823</v>
+      <c r="A3" s="19" t="s">
+        <v>834</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>835</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>824</v>
+      <c r="B4" s="20" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>825</v>
+      <c r="B5" s="20" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>826</v>
+      <c r="B6" s="20" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>827</v>
+      <c r="B7" s="20" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>828</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>829</v>
+      <c r="A8" s="19" t="s">
+        <v>840</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>830</v>
+      <c r="B9" s="20" t="s">
+        <v>842</v>
       </c>
     </row>
   </sheetData>
